--- a/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week03_14Sep.xlsx
+++ b/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week03_14Sep.xlsx
@@ -1449,7 +1449,7 @@
       <c r="I13" s="68" t="inlineStr">
         <is>
           <t>TA partners in role-plays so no pupil is exposed; teacher holds the ground rules visibly; live feedback via the cards — written work minimal and private.
-LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to EFL, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
+LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to evidence platform, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
         </is>
       </c>
       <c r="J13" s="68" t="inlineStr">
